--- a/MIP_RULE/results/model_B_piece_details.xlsx
+++ b/MIP_RULE/results/model_B_piece_details.xlsx
@@ -521,31 +521,31 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>9.25</v>
+        <v>3.05</v>
       </c>
       <c r="J2" t="n">
-        <v>9.25</v>
+        <v>3.05</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>14.59000000000003</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>15.92000000000003</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>14.59000000000003</v>
+        <v>8.390000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -569,31 +569,31 @@
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H3" t="n">
         <v>5</v>
       </c>
       <c r="I3" t="n">
-        <v>6.5</v>
+        <v>9.6</v>
       </c>
       <c r="J3" t="n">
-        <v>6.5</v>
+        <v>9.6</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>11.84</v>
+        <v>14.94</v>
       </c>
       <c r="M3" t="n">
-        <v>13.17</v>
+        <v>16.27</v>
       </c>
       <c r="N3" t="n">
-        <v>11.84</v>
+        <v>14.94</v>
       </c>
     </row>
     <row r="4">
@@ -617,31 +617,31 @@
         <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
         <v>10</v>
       </c>
       <c r="I4" t="n">
-        <v>13.05</v>
+        <v>14.6</v>
       </c>
       <c r="J4" t="n">
-        <v>13.05</v>
+        <v>14.6</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>18.39</v>
+        <v>19.94</v>
       </c>
       <c r="M4" t="n">
-        <v>19.71999999999999</v>
+        <v>21.27</v>
       </c>
       <c r="N4" t="n">
-        <v>18.39</v>
+        <v>19.94</v>
       </c>
     </row>
     <row r="5">
@@ -665,31 +665,31 @@
         <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H5" t="n">
         <v>15</v>
       </c>
       <c r="I5" t="n">
-        <v>19.6</v>
+        <v>18.05</v>
       </c>
       <c r="J5" t="n">
-        <v>19.6</v>
+        <v>18.05</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>24.94</v>
+        <v>23.39</v>
       </c>
       <c r="M5" t="n">
-        <v>26.26999999999997</v>
+        <v>24.72</v>
       </c>
       <c r="N5" t="n">
-        <v>24.94</v>
+        <v>23.39</v>
       </c>
     </row>
     <row r="6">
@@ -713,31 +713,31 @@
         <v>4</v>
       </c>
       <c r="F6" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>20</v>
       </c>
       <c r="I6" t="n">
-        <v>26.15</v>
+        <v>21.5</v>
       </c>
       <c r="J6" t="n">
-        <v>26.15</v>
+        <v>21.5</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>31.48999999999945</v>
+        <v>26.84</v>
       </c>
       <c r="M6" t="n">
-        <v>32.81999999999938</v>
+        <v>28.17</v>
       </c>
       <c r="N6" t="n">
-        <v>31.48999999999945</v>
+        <v>26.84</v>
       </c>
     </row>
     <row r="7">
@@ -761,31 +761,31 @@
         <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
         <v>25</v>
       </c>
       <c r="I7" t="n">
-        <v>32.7</v>
+        <v>26.5</v>
       </c>
       <c r="J7" t="n">
-        <v>32.7</v>
+        <v>26.5</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>38.03999999999944</v>
+        <v>31.84</v>
       </c>
       <c r="M7" t="n">
-        <v>39.36999999999993</v>
+        <v>33.16999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>38.03999999999944</v>
+        <v>31.84</v>
       </c>
     </row>
     <row r="8">
@@ -827,13 +827,13 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>37.0099999999994</v>
+        <v>37.01</v>
       </c>
       <c r="M8" t="n">
-        <v>38.52999999999999</v>
+        <v>38.53</v>
       </c>
       <c r="N8" t="n">
-        <v>37.0099999999994</v>
+        <v>37.01</v>
       </c>
     </row>
     <row r="9">
@@ -875,13 +875,13 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>43.55999999999949</v>
+        <v>43.56</v>
       </c>
       <c r="M9" t="n">
-        <v>45.07999999999999</v>
+        <v>45.07999999999997</v>
       </c>
       <c r="N9" t="n">
-        <v>43.55999999999949</v>
+        <v>43.56</v>
       </c>
     </row>
     <row r="10">
@@ -962,22 +962,22 @@
         <v>45</v>
       </c>
       <c r="I11" t="n">
-        <v>51.15</v>
+        <v>46.5</v>
       </c>
       <c r="J11" t="n">
-        <v>51.15</v>
+        <v>46.5</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>56.66</v>
+        <v>52.00999999999996</v>
       </c>
       <c r="M11" t="n">
-        <v>58.17999999999999</v>
+        <v>53.52999999999997</v>
       </c>
       <c r="N11" t="n">
-        <v>56.66</v>
+        <v>52.00999999999996</v>
       </c>
     </row>
     <row r="12">
@@ -1010,22 +1010,22 @@
         <v>50</v>
       </c>
       <c r="I12" t="n">
-        <v>57.7</v>
+        <v>53.05</v>
       </c>
       <c r="J12" t="n">
-        <v>57.7</v>
+        <v>53.05</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>63.20999999999948</v>
+        <v>58.56</v>
       </c>
       <c r="M12" t="n">
-        <v>64.72999999999843</v>
+        <v>60.07999999999998</v>
       </c>
       <c r="N12" t="n">
-        <v>63.20999999999948</v>
+        <v>58.56</v>
       </c>
     </row>
     <row r="13">
@@ -1058,22 +1058,22 @@
         <v>55</v>
       </c>
       <c r="I13" t="n">
-        <v>64.25</v>
+        <v>59.6</v>
       </c>
       <c r="J13" t="n">
-        <v>64.25</v>
+        <v>59.6</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>69.75999999999998</v>
+        <v>65.11</v>
       </c>
       <c r="M13" t="n">
-        <v>71.27999999999858</v>
+        <v>66.63</v>
       </c>
       <c r="N13" t="n">
-        <v>69.75999999999998</v>
+        <v>65.11</v>
       </c>
     </row>
     <row r="14">
@@ -1115,13 +1115,13 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>67.31999999999934</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="M14" t="n">
         <v>69.15000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>67.31999999999934</v>
+        <v>67.31999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1211,13 +1211,13 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>80.42000000000002</v>
+        <v>80.41999999999999</v>
       </c>
       <c r="M16" t="n">
         <v>82.25</v>
       </c>
       <c r="N16" t="n">
-        <v>80.42000000000002</v>
+        <v>80.41999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -1241,7 +1241,7 @@
         <v>15</v>
       </c>
       <c r="F17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G17" t="n">
         <v>3</v>
@@ -1250,22 +1250,22 @@
         <v>75</v>
       </c>
       <c r="I17" t="n">
-        <v>81.15000000000001</v>
+        <v>76.5</v>
       </c>
       <c r="J17" t="n">
-        <v>81.15000000000001</v>
+        <v>76.5</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>86.97</v>
+        <v>82.31999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>88.8</v>
+        <v>84.15000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>86.97</v>
+        <v>82.31999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -1298,22 +1298,22 @@
         <v>80</v>
       </c>
       <c r="I18" t="n">
-        <v>87.7</v>
+        <v>83.05</v>
       </c>
       <c r="J18" t="n">
-        <v>87.7</v>
+        <v>83.05</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>93.52000000000001</v>
+        <v>88.87</v>
       </c>
       <c r="M18" t="n">
-        <v>95.34999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="N18" t="n">
-        <v>93.52000000000001</v>
+        <v>88.87</v>
       </c>
     </row>
     <row r="19">
@@ -1346,22 +1346,22 @@
         <v>85</v>
       </c>
       <c r="I19" t="n">
-        <v>94.25</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>94.25</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>100.07</v>
+        <v>95.41999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>101.9</v>
+        <v>97.25</v>
       </c>
       <c r="N19" t="n">
-        <v>100.07</v>
+        <v>95.41999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1403,13 +1403,13 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>97.31999999999931</v>
+        <v>97.31999999999999</v>
       </c>
       <c r="M20" t="n">
         <v>99.15000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>97.31999999999931</v>
+        <v>97.31999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -1529,7 +1529,7 @@
         <v>21</v>
       </c>
       <c r="F23" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G23" t="n">
         <v>3</v>
@@ -1538,22 +1538,22 @@
         <v>105</v>
       </c>
       <c r="I23" t="n">
-        <v>111.15</v>
+        <v>106.5</v>
       </c>
       <c r="J23" t="n">
-        <v>111.15</v>
+        <v>106.5</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>116.97</v>
+        <v>112.32</v>
       </c>
       <c r="M23" t="n">
-        <v>118.8</v>
+        <v>114.15</v>
       </c>
       <c r="N23" t="n">
-        <v>116.97</v>
+        <v>112.32</v>
       </c>
     </row>
     <row r="24">
@@ -1586,22 +1586,22 @@
         <v>110</v>
       </c>
       <c r="I24" t="n">
-        <v>117.7</v>
+        <v>113.05</v>
       </c>
       <c r="J24" t="n">
-        <v>117.7</v>
+        <v>113.05</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>123.52</v>
+        <v>118.87</v>
       </c>
       <c r="M24" t="n">
-        <v>125.35</v>
+        <v>120.7</v>
       </c>
       <c r="N24" t="n">
-        <v>123.52</v>
+        <v>118.87</v>
       </c>
     </row>
     <row r="25">
@@ -1634,22 +1634,22 @@
         <v>115</v>
       </c>
       <c r="I25" t="n">
-        <v>124.25</v>
+        <v>119.6</v>
       </c>
       <c r="J25" t="n">
-        <v>124.25</v>
+        <v>119.6</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>130.07</v>
+        <v>125.42</v>
       </c>
       <c r="M25" t="n">
-        <v>131.9</v>
+        <v>127.25</v>
       </c>
       <c r="N25" t="n">
-        <v>130.07</v>
+        <v>125.42</v>
       </c>
     </row>
     <row r="26">
@@ -1673,31 +1673,31 @@
         <v>24</v>
       </c>
       <c r="F26" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="G26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>120</v>
       </c>
       <c r="I26" t="n">
-        <v>126.15</v>
+        <v>121.5</v>
       </c>
       <c r="J26" t="n">
-        <v>126.15</v>
+        <v>121.5</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>132</v>
+        <v>127.35</v>
       </c>
       <c r="M26" t="n">
-        <v>133.84</v>
+        <v>129.19</v>
       </c>
       <c r="N26" t="n">
-        <v>132</v>
+        <v>127.35</v>
       </c>
     </row>
     <row r="27">
@@ -1721,7 +1721,7 @@
         <v>25</v>
       </c>
       <c r="F27" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
@@ -1790,7 +1790,7 @@
         <v>140.45</v>
       </c>
       <c r="M28" t="n">
-        <v>142.2899999999995</v>
+        <v>142.29</v>
       </c>
       <c r="N28" t="n">
         <v>140.45</v>
@@ -1817,10 +1817,10 @@
         <v>27</v>
       </c>
       <c r="F29" t="n">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H29" t="n">
         <v>135</v>
@@ -1874,22 +1874,22 @@
         <v>140</v>
       </c>
       <c r="I30" t="n">
-        <v>147.7</v>
+        <v>143.05</v>
       </c>
       <c r="J30" t="n">
-        <v>147.7</v>
+        <v>143.05</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>153.55</v>
+        <v>148.9</v>
       </c>
       <c r="M30" t="n">
-        <v>155.39</v>
+        <v>150.74</v>
       </c>
       <c r="N30" t="n">
-        <v>153.55</v>
+        <v>148.9</v>
       </c>
     </row>
     <row r="31">
@@ -1922,22 +1922,22 @@
         <v>145</v>
       </c>
       <c r="I31" t="n">
-        <v>154.25</v>
+        <v>149.6</v>
       </c>
       <c r="J31" t="n">
-        <v>154.25</v>
+        <v>149.6</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>160.1</v>
+        <v>155.45</v>
       </c>
       <c r="M31" t="n">
-        <v>161.940000000002</v>
+        <v>157.29</v>
       </c>
       <c r="N31" t="n">
-        <v>167.7899999999979</v>
+        <v>163.14</v>
       </c>
     </row>
     <row r="32">
@@ -1970,22 +1970,22 @@
         <v>150</v>
       </c>
       <c r="I32" t="n">
-        <v>159.25</v>
+        <v>154.6</v>
       </c>
       <c r="J32" t="n">
-        <v>161.9399999999999</v>
+        <v>157.29</v>
       </c>
       <c r="K32" t="n">
         <v>2.689999999999941</v>
       </c>
       <c r="L32" t="n">
-        <v>167.7899999999999</v>
+        <v>163.14</v>
       </c>
       <c r="M32" t="n">
-        <v>169.6299999999999</v>
+        <v>164.98</v>
       </c>
       <c r="N32" t="n">
-        <v>167.7899999999979</v>
+        <v>163.14</v>
       </c>
     </row>
     <row r="33">
@@ -2030,7 +2030,7 @@
         <v>162.35</v>
       </c>
       <c r="M33" t="n">
-        <v>164.1899999999994</v>
+        <v>164.19</v>
       </c>
       <c r="N33" t="n">
         <v>162.35</v>
@@ -2057,7 +2057,7 @@
         <v>32</v>
       </c>
       <c r="F34" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G34" t="n">
         <v>1</v>
@@ -2081,7 +2081,7 @@
         <v>170.74</v>
       </c>
       <c r="N34" t="n">
-        <v>176.5899999999943</v>
+        <v>176.59</v>
       </c>
     </row>
     <row r="35">
@@ -2105,7 +2105,7 @@
         <v>33</v>
       </c>
       <c r="F35" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G35" t="n">
         <v>1</v>
@@ -2117,19 +2117,19 @@
         <v>168.05</v>
       </c>
       <c r="J35" t="n">
-        <v>170.7399999999944</v>
+        <v>170.74</v>
       </c>
       <c r="K35" t="n">
-        <v>2.689999999994342</v>
+        <v>2.689999999999969</v>
       </c>
       <c r="L35" t="n">
-        <v>176.5899999999943</v>
+        <v>176.59</v>
       </c>
       <c r="M35" t="n">
-        <v>178.4299999999944</v>
+        <v>178.43</v>
       </c>
       <c r="N35" t="n">
-        <v>176.5899999999943</v>
+        <v>176.59</v>
       </c>
     </row>
     <row r="36">
@@ -2174,10 +2174,10 @@
         <v>180.45</v>
       </c>
       <c r="M36" t="n">
-        <v>182.2899999999992</v>
+        <v>182.29</v>
       </c>
       <c r="N36" t="n">
-        <v>188.1399999999995</v>
+        <v>188.14</v>
       </c>
     </row>
     <row r="37">
@@ -2225,7 +2225,7 @@
         <v>189.98</v>
       </c>
       <c r="N37" t="n">
-        <v>188.1399999999995</v>
+        <v>188.14</v>
       </c>
     </row>
     <row r="38">
@@ -2258,22 +2258,22 @@
         <v>180</v>
       </c>
       <c r="I38" t="n">
-        <v>186.15</v>
+        <v>181.5</v>
       </c>
       <c r="J38" t="n">
-        <v>186.15</v>
+        <v>181.5</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>192</v>
+        <v>187.35</v>
       </c>
       <c r="M38" t="n">
-        <v>193.8399999999999</v>
+        <v>189.1899999999997</v>
       </c>
       <c r="N38" t="n">
-        <v>192</v>
+        <v>187.35</v>
       </c>
     </row>
     <row r="39">
@@ -2306,22 +2306,22 @@
         <v>185</v>
       </c>
       <c r="I39" t="n">
-        <v>192.7</v>
+        <v>188.05</v>
       </c>
       <c r="J39" t="n">
-        <v>192.7</v>
+        <v>188.05</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>198.55</v>
+        <v>193.9</v>
       </c>
       <c r="M39" t="n">
-        <v>200.3899999999999</v>
+        <v>195.74</v>
       </c>
       <c r="N39" t="n">
-        <v>198.55</v>
+        <v>193.9</v>
       </c>
     </row>
     <row r="40">
@@ -2354,22 +2354,22 @@
         <v>190</v>
       </c>
       <c r="I40" t="n">
-        <v>199.25</v>
+        <v>194.6</v>
       </c>
       <c r="J40" t="n">
-        <v>199.25</v>
+        <v>194.6</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>205.1</v>
+        <v>200.45</v>
       </c>
       <c r="M40" t="n">
-        <v>206.9399999999999</v>
+        <v>202.2899999999999</v>
       </c>
       <c r="N40" t="n">
-        <v>205.1</v>
+        <v>200.45</v>
       </c>
     </row>
     <row r="41">
@@ -2459,13 +2459,13 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>209.2299999999998</v>
+        <v>209.23</v>
       </c>
       <c r="M42" t="n">
-        <v>211.4099999999999</v>
+        <v>211.41</v>
       </c>
       <c r="N42" t="n">
-        <v>209.2299999999998</v>
+        <v>209.23</v>
       </c>
     </row>
     <row r="43">
@@ -2489,7 +2489,7 @@
         <v>41</v>
       </c>
       <c r="F43" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G43" t="n">
         <v>2</v>
@@ -2546,22 +2546,22 @@
         <v>210</v>
       </c>
       <c r="I44" t="n">
-        <v>216.15</v>
+        <v>211.5</v>
       </c>
       <c r="J44" t="n">
-        <v>216.15</v>
+        <v>211.5</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>222.3299999999999</v>
+        <v>217.68</v>
       </c>
       <c r="M44" t="n">
-        <v>224.5099999999999</v>
+        <v>219.86</v>
       </c>
       <c r="N44" t="n">
-        <v>222.3299999999999</v>
+        <v>217.68</v>
       </c>
     </row>
     <row r="45">
@@ -2585,7 +2585,7 @@
         <v>43</v>
       </c>
       <c r="F45" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="G45" t="n">
         <v>4</v>
@@ -2594,22 +2594,22 @@
         <v>215</v>
       </c>
       <c r="I45" t="n">
-        <v>222.7</v>
+        <v>218.05</v>
       </c>
       <c r="J45" t="n">
-        <v>222.7</v>
+        <v>218.05</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>228.8799999999999</v>
+        <v>224.23</v>
       </c>
       <c r="M45" t="n">
-        <v>231.0599999999999</v>
+        <v>226.41</v>
       </c>
       <c r="N45" t="n">
-        <v>228.8799999999999</v>
+        <v>224.23</v>
       </c>
     </row>
     <row r="46">
@@ -2642,22 +2642,22 @@
         <v>220</v>
       </c>
       <c r="I46" t="n">
-        <v>229.25</v>
+        <v>224.6</v>
       </c>
       <c r="J46" t="n">
-        <v>229.25</v>
+        <v>224.6</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>235.43</v>
+        <v>230.78</v>
       </c>
       <c r="M46" t="n">
-        <v>237.6099999999999</v>
+        <v>232.9599999999999</v>
       </c>
       <c r="N46" t="n">
-        <v>235.43</v>
+        <v>230.78</v>
       </c>
     </row>
     <row r="47">
@@ -2702,7 +2702,7 @@
         <v>232.68</v>
       </c>
       <c r="M47" t="n">
-        <v>234.8599999999993</v>
+        <v>234.86</v>
       </c>
       <c r="N47" t="n">
         <v>232.68</v>
@@ -2747,13 +2747,13 @@
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>239.2299999999994</v>
+        <v>239.23</v>
       </c>
       <c r="M48" t="n">
-        <v>241.4099999999993</v>
+        <v>241.41</v>
       </c>
       <c r="N48" t="n">
-        <v>239.2299999999994</v>
+        <v>239.23</v>
       </c>
     </row>
     <row r="49">
@@ -2777,7 +2777,7 @@
         <v>47</v>
       </c>
       <c r="F49" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G49" t="n">
         <v>2</v>
@@ -2795,13 +2795,13 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>245.7799999999999</v>
+        <v>245.78</v>
       </c>
       <c r="M49" t="n">
-        <v>247.9599999999999</v>
+        <v>247.96</v>
       </c>
       <c r="N49" t="n">
-        <v>245.7799999999999</v>
+        <v>245.78</v>
       </c>
     </row>
     <row r="50">
@@ -2834,22 +2834,22 @@
         <v>240</v>
       </c>
       <c r="I50" t="n">
-        <v>246.15</v>
+        <v>241.5</v>
       </c>
       <c r="J50" t="n">
-        <v>246.15</v>
+        <v>241.5</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>252.33</v>
+        <v>247.68</v>
       </c>
       <c r="M50" t="n">
-        <v>254.5099999999998</v>
+        <v>249.86</v>
       </c>
       <c r="N50" t="n">
-        <v>252.33</v>
+        <v>247.68</v>
       </c>
     </row>
     <row r="51">
@@ -2873,7 +2873,7 @@
         <v>49</v>
       </c>
       <c r="F51" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="G51" t="n">
         <v>4</v>
@@ -2882,22 +2882,22 @@
         <v>245</v>
       </c>
       <c r="I51" t="n">
-        <v>252.7</v>
+        <v>248.05</v>
       </c>
       <c r="J51" t="n">
-        <v>252.7</v>
+        <v>248.05</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>258.8799999999999</v>
+        <v>254.23</v>
       </c>
       <c r="M51" t="n">
-        <v>261.06</v>
+        <v>256.41</v>
       </c>
       <c r="N51" t="n">
-        <v>258.8799999999999</v>
+        <v>254.23</v>
       </c>
     </row>
     <row r="52">
@@ -2930,22 +2930,22 @@
         <v>250</v>
       </c>
       <c r="I52" t="n">
-        <v>259.25</v>
+        <v>254.6</v>
       </c>
       <c r="J52" t="n">
-        <v>259.25</v>
+        <v>254.6</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>265.43</v>
+        <v>260.78</v>
       </c>
       <c r="M52" t="n">
-        <v>267.61</v>
+        <v>262.96</v>
       </c>
       <c r="N52" t="n">
-        <v>273.7899999999999</v>
+        <v>269.14</v>
       </c>
     </row>
     <row r="53">
@@ -2978,22 +2978,22 @@
         <v>255</v>
       </c>
       <c r="I53" t="n">
-        <v>264.25</v>
+        <v>259.6</v>
       </c>
       <c r="J53" t="n">
-        <v>267.61</v>
+        <v>262.96</v>
       </c>
       <c r="K53" t="n">
         <v>3.359999999999957</v>
       </c>
       <c r="L53" t="n">
-        <v>273.79</v>
+        <v>269.14</v>
       </c>
       <c r="M53" t="n">
-        <v>275.97</v>
+        <v>271.32</v>
       </c>
       <c r="N53" t="n">
-        <v>273.7899999999999</v>
+        <v>269.14</v>
       </c>
     </row>
     <row r="54">
@@ -3017,31 +3017,31 @@
         <v>52</v>
       </c>
       <c r="F54" t="n">
-        <v>73</v>
+        <v>10</v>
       </c>
       <c r="G54" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
         <v>260</v>
       </c>
       <c r="I54" t="n">
-        <v>267.7</v>
+        <v>261.5</v>
       </c>
       <c r="J54" t="n">
-        <v>267.7</v>
+        <v>261.5</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>274.01</v>
+        <v>267.81</v>
       </c>
       <c r="M54" t="n">
-        <v>276.3299999999998</v>
+        <v>270.13</v>
       </c>
       <c r="N54" t="n">
-        <v>274.01</v>
+        <v>267.81</v>
       </c>
     </row>
     <row r="55">
@@ -3083,13 +3083,13 @@
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>274.3599999999999</v>
+        <v>274.36</v>
       </c>
       <c r="M55" t="n">
-        <v>276.6799999999999</v>
+        <v>276.68</v>
       </c>
       <c r="N55" t="n">
-        <v>274.3599999999999</v>
+        <v>274.36</v>
       </c>
     </row>
     <row r="56">
@@ -3113,7 +3113,7 @@
         <v>54</v>
       </c>
       <c r="F56" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G56" t="n">
         <v>2</v>
@@ -3134,7 +3134,7 @@
         <v>280.91</v>
       </c>
       <c r="M56" t="n">
-        <v>283.2299999999999</v>
+        <v>283.23</v>
       </c>
       <c r="N56" t="n">
         <v>280.91</v>
@@ -3161,7 +3161,7 @@
         <v>55</v>
       </c>
       <c r="F57" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G57" t="n">
         <v>3</v>
@@ -3170,22 +3170,22 @@
         <v>275</v>
       </c>
       <c r="I57" t="n">
-        <v>281.15</v>
+        <v>276.5</v>
       </c>
       <c r="J57" t="n">
-        <v>281.15</v>
+        <v>276.5</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>287.46</v>
+        <v>282.81</v>
       </c>
       <c r="M57" t="n">
-        <v>289.7799999999999</v>
+        <v>285.13</v>
       </c>
       <c r="N57" t="n">
-        <v>287.46</v>
+        <v>282.81</v>
       </c>
     </row>
     <row r="58">
@@ -3209,31 +3209,31 @@
         <v>56</v>
       </c>
       <c r="F58" t="n">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H58" t="n">
         <v>280</v>
       </c>
       <c r="I58" t="n">
-        <v>281.5</v>
+        <v>283.05</v>
       </c>
       <c r="J58" t="n">
-        <v>281.5</v>
+        <v>283.05</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>287.81</v>
+        <v>289.36</v>
       </c>
       <c r="M58" t="n">
-        <v>290.1299999999993</v>
+        <v>291.68</v>
       </c>
       <c r="N58" t="n">
-        <v>287.81</v>
+        <v>289.36</v>
       </c>
     </row>
     <row r="59">
@@ -3257,7 +3257,7 @@
         <v>57</v>
       </c>
       <c r="F59" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G59" t="n">
         <v>5</v>
@@ -3266,22 +3266,22 @@
         <v>285</v>
       </c>
       <c r="I59" t="n">
-        <v>294.25</v>
+        <v>289.6</v>
       </c>
       <c r="J59" t="n">
-        <v>294.25</v>
+        <v>289.6</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>300.56</v>
+        <v>295.91</v>
       </c>
       <c r="M59" t="n">
-        <v>302.8799999999999</v>
+        <v>298.23</v>
       </c>
       <c r="N59" t="n">
-        <v>300.56</v>
+        <v>295.91</v>
       </c>
     </row>
     <row r="60">
@@ -3305,7 +3305,7 @@
         <v>58</v>
       </c>
       <c r="F60" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -3323,13 +3323,13 @@
         <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>297.8099999999999</v>
+        <v>297.81</v>
       </c>
       <c r="M60" t="n">
-        <v>300.1299999999999</v>
+        <v>300.13</v>
       </c>
       <c r="N60" t="n">
-        <v>297.8099999999999</v>
+        <v>297.81</v>
       </c>
     </row>
     <row r="61">
@@ -3371,13 +3371,13 @@
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>304.3599999999999</v>
+        <v>304.36</v>
       </c>
       <c r="M61" t="n">
-        <v>306.6799999999998</v>
+        <v>306.68</v>
       </c>
       <c r="N61" t="n">
-        <v>304.3599999999999</v>
+        <v>304.36</v>
       </c>
     </row>
     <row r="62">
@@ -3422,7 +3422,7 @@
         <v>310.91</v>
       </c>
       <c r="M62" t="n">
-        <v>313.2299999999997</v>
+        <v>313.23</v>
       </c>
       <c r="N62" t="n">
         <v>310.91</v>
@@ -3458,22 +3458,22 @@
         <v>305</v>
       </c>
       <c r="I63" t="n">
-        <v>311.15</v>
+        <v>306.5</v>
       </c>
       <c r="J63" t="n">
-        <v>311.15</v>
+        <v>306.5</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>317.46</v>
+        <v>312.81</v>
       </c>
       <c r="M63" t="n">
-        <v>319.7799999999999</v>
+        <v>315.13</v>
       </c>
       <c r="N63" t="n">
-        <v>317.46</v>
+        <v>312.81</v>
       </c>
     </row>
     <row r="64">
@@ -3497,7 +3497,7 @@
         <v>62</v>
       </c>
       <c r="F64" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G64" t="n">
         <v>4</v>
@@ -3506,22 +3506,22 @@
         <v>310</v>
       </c>
       <c r="I64" t="n">
-        <v>317.7</v>
+        <v>313.05</v>
       </c>
       <c r="J64" t="n">
-        <v>317.7</v>
+        <v>313.05</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>324.01</v>
+        <v>319.36</v>
       </c>
       <c r="M64" t="n">
-        <v>326.3299999999999</v>
+        <v>321.68</v>
       </c>
       <c r="N64" t="n">
-        <v>324.01</v>
+        <v>319.36</v>
       </c>
     </row>
     <row r="65">
@@ -3554,22 +3554,22 @@
         <v>315</v>
       </c>
       <c r="I65" t="n">
-        <v>324.25</v>
+        <v>319.6</v>
       </c>
       <c r="J65" t="n">
-        <v>324.25</v>
+        <v>319.6</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>330.5599999999999</v>
+        <v>325.9099999999997</v>
       </c>
       <c r="M65" t="n">
-        <v>332.88</v>
+        <v>328.2299999999997</v>
       </c>
       <c r="N65" t="n">
-        <v>330.5599999999999</v>
+        <v>325.9099999999997</v>
       </c>
     </row>
     <row r="66">
@@ -3611,13 +3611,13 @@
         <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>327.8099999999999</v>
+        <v>327.81</v>
       </c>
       <c r="M66" t="n">
-        <v>330.1299999999999</v>
+        <v>330.13</v>
       </c>
       <c r="N66" t="n">
-        <v>327.8099999999999</v>
+        <v>327.81</v>
       </c>
     </row>
     <row r="67">
@@ -3641,31 +3641,31 @@
         <v>65</v>
       </c>
       <c r="F67" t="n">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="G67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H67" t="n">
         <v>325</v>
       </c>
       <c r="I67" t="n">
-        <v>332.7</v>
+        <v>328.05</v>
       </c>
       <c r="J67" t="n">
-        <v>332.7</v>
+        <v>328.05</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>339.01</v>
+        <v>334.36</v>
       </c>
       <c r="M67" t="n">
-        <v>341.3299999999994</v>
+        <v>336.68</v>
       </c>
       <c r="N67" t="n">
-        <v>339.01</v>
+        <v>334.36</v>
       </c>
     </row>
     <row r="68">
@@ -3689,7 +3689,7 @@
         <v>66</v>
       </c>
       <c r="F68" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G68" t="n">
         <v>2</v>
@@ -3707,13 +3707,13 @@
         <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>340.9099999999999</v>
+        <v>340.91</v>
       </c>
       <c r="M68" t="n">
         <v>343.23</v>
       </c>
       <c r="N68" t="n">
-        <v>340.9099999999999</v>
+        <v>340.91</v>
       </c>
     </row>
     <row r="69">
@@ -3737,7 +3737,7 @@
         <v>67</v>
       </c>
       <c r="F69" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G69" t="n">
         <v>3</v>
@@ -3746,22 +3746,22 @@
         <v>335</v>
       </c>
       <c r="I69" t="n">
-        <v>341.15</v>
+        <v>336.5</v>
       </c>
       <c r="J69" t="n">
-        <v>341.15</v>
+        <v>336.5</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>347.46</v>
+        <v>342.81</v>
       </c>
       <c r="M69" t="n">
-        <v>349.7799999999998</v>
+        <v>345.13</v>
       </c>
       <c r="N69" t="n">
-        <v>347.46</v>
+        <v>342.81</v>
       </c>
     </row>
     <row r="70">
@@ -3785,10 +3785,10 @@
         <v>68</v>
       </c>
       <c r="F70" t="n">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="G70" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H70" t="n">
         <v>340</v>
@@ -3806,7 +3806,7 @@
         <v>349.36</v>
       </c>
       <c r="M70" t="n">
-        <v>351.6799999999998</v>
+        <v>351.6799999999999</v>
       </c>
       <c r="N70" t="n">
         <v>349.36</v>
@@ -3833,7 +3833,7 @@
         <v>69</v>
       </c>
       <c r="F71" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G71" t="n">
         <v>5</v>
@@ -3842,22 +3842,22 @@
         <v>345</v>
       </c>
       <c r="I71" t="n">
-        <v>354.25</v>
+        <v>349.6</v>
       </c>
       <c r="J71" t="n">
-        <v>354.25</v>
+        <v>349.6</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>360.5599999999999</v>
+        <v>355.91</v>
       </c>
       <c r="M71" t="n">
-        <v>362.8799999999999</v>
+        <v>358.2299999999999</v>
       </c>
       <c r="N71" t="n">
-        <v>360.5599999999999</v>
+        <v>355.91</v>
       </c>
     </row>
     <row r="72">
@@ -3881,7 +3881,7 @@
         <v>70</v>
       </c>
       <c r="F72" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -3899,13 +3899,13 @@
         <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>357.8099999999999</v>
+        <v>357.81</v>
       </c>
       <c r="M72" t="n">
-        <v>360.1299999999999</v>
+        <v>360.13</v>
       </c>
       <c r="N72" t="n">
-        <v>357.8099999999999</v>
+        <v>357.81</v>
       </c>
     </row>
     <row r="73">
@@ -3929,31 +3929,31 @@
         <v>71</v>
       </c>
       <c r="F73" t="n">
-        <v>87</v>
+        <v>28</v>
       </c>
       <c r="G73" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H73" t="n">
         <v>355</v>
       </c>
       <c r="I73" t="n">
-        <v>364.25</v>
+        <v>358.05</v>
       </c>
       <c r="J73" t="n">
-        <v>364.25</v>
+        <v>358.05</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>370.56</v>
+        <v>364.36</v>
       </c>
       <c r="M73" t="n">
-        <v>372.8799999999989</v>
+        <v>366.6799999999999</v>
       </c>
       <c r="N73" t="n">
-        <v>370.56</v>
+        <v>364.36</v>
       </c>
     </row>
     <row r="74">
@@ -3977,31 +3977,31 @@
         <v>72</v>
       </c>
       <c r="F74" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="G74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H74" t="n">
         <v>360</v>
       </c>
       <c r="I74" t="n">
-        <v>363.05</v>
+        <v>364.6</v>
       </c>
       <c r="J74" t="n">
-        <v>363.05</v>
+        <v>364.6</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>369.36</v>
+        <v>370.91</v>
       </c>
       <c r="M74" t="n">
-        <v>371.6799999999998</v>
+        <v>373.2299999999999</v>
       </c>
       <c r="N74" t="n">
-        <v>369.36</v>
+        <v>370.91</v>
       </c>
     </row>
     <row r="75">
@@ -4034,22 +4034,22 @@
         <v>365</v>
       </c>
       <c r="I75" t="n">
-        <v>371.15</v>
+        <v>366.5</v>
       </c>
       <c r="J75" t="n">
-        <v>371.15</v>
+        <v>366.5</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>377.4599999999999</v>
+        <v>372.81</v>
       </c>
       <c r="M75" t="n">
-        <v>379.7799999999999</v>
+        <v>375.13</v>
       </c>
       <c r="N75" t="n">
-        <v>377.4599999999999</v>
+        <v>372.81</v>
       </c>
     </row>
     <row r="76">
@@ -4073,7 +4073,7 @@
         <v>74</v>
       </c>
       <c r="F76" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G76" t="n">
         <v>4</v>
@@ -4082,22 +4082,22 @@
         <v>370</v>
       </c>
       <c r="I76" t="n">
-        <v>377.7</v>
+        <v>373.05</v>
       </c>
       <c r="J76" t="n">
-        <v>377.7</v>
+        <v>373.05</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>384.0099999999999</v>
+        <v>379.36</v>
       </c>
       <c r="M76" t="n">
-        <v>386.33</v>
+        <v>381.6799999999999</v>
       </c>
       <c r="N76" t="n">
-        <v>384.0099999999999</v>
+        <v>379.36</v>
       </c>
     </row>
     <row r="77">
@@ -4121,10 +4121,10 @@
         <v>75</v>
       </c>
       <c r="F77" t="n">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="G77" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H77" t="n">
         <v>375</v>
@@ -4142,7 +4142,7 @@
         <v>385.91</v>
       </c>
       <c r="M77" t="n">
-        <v>388.2299999999983</v>
+        <v>388.2299999999999</v>
       </c>
       <c r="N77" t="n">
         <v>385.91</v>
@@ -4169,31 +4169,31 @@
         <v>76</v>
       </c>
       <c r="F78" t="n">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="G78" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H78" t="n">
         <v>380</v>
       </c>
       <c r="I78" t="n">
-        <v>389.25</v>
+        <v>383.05</v>
       </c>
       <c r="J78" t="n">
-        <v>389.25</v>
+        <v>383.05</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>395.76</v>
+        <v>389.56</v>
       </c>
       <c r="M78" t="n">
-        <v>398.2799999999997</v>
+        <v>392.08</v>
       </c>
       <c r="N78" t="n">
-        <v>395.76</v>
+        <v>389.56</v>
       </c>
     </row>
     <row r="79">
@@ -4217,31 +4217,31 @@
         <v>77</v>
       </c>
       <c r="F79" t="n">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="G79" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H79" t="n">
         <v>385</v>
       </c>
       <c r="I79" t="n">
-        <v>392.7</v>
+        <v>389.6</v>
       </c>
       <c r="J79" t="n">
-        <v>392.7</v>
+        <v>389.6</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>399.2099999999998</v>
+        <v>396.11</v>
       </c>
       <c r="M79" t="n">
-        <v>401.7299999999998</v>
+        <v>398.63</v>
       </c>
       <c r="N79" t="n">
-        <v>399.2099999999998</v>
+        <v>396.11</v>
       </c>
     </row>
     <row r="80">
@@ -4265,7 +4265,7 @@
         <v>78</v>
       </c>
       <c r="F80" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G80" t="n">
         <v>3</v>
@@ -4274,22 +4274,22 @@
         <v>390</v>
       </c>
       <c r="I80" t="n">
-        <v>396.15</v>
+        <v>391.5</v>
       </c>
       <c r="J80" t="n">
-        <v>396.15</v>
+        <v>391.5</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>402.6599999999998</v>
+        <v>398.01</v>
       </c>
       <c r="M80" t="n">
-        <v>405.1799999999998</v>
+        <v>400.53</v>
       </c>
       <c r="N80" t="n">
-        <v>402.6599999999998</v>
+        <v>398.01</v>
       </c>
     </row>
     <row r="81">
@@ -4331,13 +4331,13 @@
         <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>406.1099999999998</v>
+        <v>406.11</v>
       </c>
       <c r="M81" t="n">
-        <v>408.6299999999998</v>
+        <v>408.63</v>
       </c>
       <c r="N81" t="n">
-        <v>406.1099999999998</v>
+        <v>406.11</v>
       </c>
     </row>
     <row r="82">
@@ -4361,10 +4361,10 @@
         <v>80</v>
       </c>
       <c r="F82" t="n">
-        <v>29</v>
+        <v>74</v>
       </c>
       <c r="G82" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H82" t="n">
         <v>400</v>
@@ -4379,13 +4379,13 @@
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>409.5599999999998</v>
+        <v>409.56</v>
       </c>
       <c r="M82" t="n">
-        <v>412.0799999999998</v>
+        <v>412.0799999999999</v>
       </c>
       <c r="N82" t="n">
-        <v>409.5599999999998</v>
+        <v>409.56</v>
       </c>
     </row>
     <row r="83">
@@ -4409,7 +4409,7 @@
         <v>81</v>
       </c>
       <c r="F83" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -4427,13 +4427,13 @@
         <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>413.0099999999998</v>
+        <v>413.01</v>
       </c>
       <c r="M83" t="n">
-        <v>415.5299999999998</v>
+        <v>415.5299999999999</v>
       </c>
       <c r="N83" t="n">
-        <v>413.0099999999998</v>
+        <v>413.01</v>
       </c>
     </row>
     <row r="84">
@@ -4466,22 +4466,22 @@
         <v>410</v>
       </c>
       <c r="I84" t="n">
-        <v>419.25</v>
+        <v>414.6</v>
       </c>
       <c r="J84" t="n">
-        <v>419.25</v>
+        <v>414.6</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>425.76</v>
+        <v>421.11</v>
       </c>
       <c r="M84" t="n">
-        <v>428.2799999999989</v>
+        <v>423.63</v>
       </c>
       <c r="N84" t="n">
-        <v>425.76</v>
+        <v>421.11</v>
       </c>
     </row>
     <row r="85">
@@ -4514,22 +4514,22 @@
         <v>415</v>
       </c>
       <c r="I85" t="n">
-        <v>422.7</v>
+        <v>418.05</v>
       </c>
       <c r="J85" t="n">
-        <v>422.7</v>
+        <v>418.05</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>429.21</v>
+        <v>424.56</v>
       </c>
       <c r="M85" t="n">
-        <v>431.73</v>
+        <v>427.08</v>
       </c>
       <c r="N85" t="n">
-        <v>429.21</v>
+        <v>424.56</v>
       </c>
     </row>
     <row r="86">
@@ -4553,7 +4553,7 @@
         <v>84</v>
       </c>
       <c r="F86" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G86" t="n">
         <v>3</v>
@@ -4562,22 +4562,22 @@
         <v>420</v>
       </c>
       <c r="I86" t="n">
-        <v>426.15</v>
+        <v>421.5</v>
       </c>
       <c r="J86" t="n">
-        <v>426.15</v>
+        <v>421.5</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>432.6599999999998</v>
+        <v>428.01</v>
       </c>
       <c r="M86" t="n">
-        <v>435.1799999999998</v>
+        <v>430.53</v>
       </c>
       <c r="N86" t="n">
-        <v>432.6599999999998</v>
+        <v>428.01</v>
       </c>
     </row>
     <row r="87">
@@ -4601,7 +4601,7 @@
         <v>85</v>
       </c>
       <c r="F87" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G87" t="n">
         <v>2</v>
@@ -4619,13 +4619,13 @@
         <v>0</v>
       </c>
       <c r="L87" t="n">
-        <v>436.1099999999998</v>
+        <v>436.11</v>
       </c>
       <c r="M87" t="n">
         <v>438.63</v>
       </c>
       <c r="N87" t="n">
-        <v>436.1099999999998</v>
+        <v>436.11</v>
       </c>
     </row>
     <row r="88">
@@ -4667,13 +4667,13 @@
         <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>439.5599999999998</v>
+        <v>439.56</v>
       </c>
       <c r="M88" t="n">
         <v>442.08</v>
       </c>
       <c r="N88" t="n">
-        <v>439.5599999999998</v>
+        <v>439.56</v>
       </c>
     </row>
     <row r="89">
@@ -4697,7 +4697,7 @@
         <v>87</v>
       </c>
       <c r="F89" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -4715,13 +4715,13 @@
         <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>443.01</v>
+        <v>443.0099999999994</v>
       </c>
       <c r="M89" t="n">
-        <v>445.5299999999984</v>
+        <v>445.5299999999994</v>
       </c>
       <c r="N89" t="n">
-        <v>443.01</v>
+        <v>443.0099999999994</v>
       </c>
     </row>
     <row r="90">
@@ -4745,7 +4745,7 @@
         <v>88</v>
       </c>
       <c r="F90" t="n">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G90" t="n">
         <v>5</v>
@@ -4754,22 +4754,22 @@
         <v>440</v>
       </c>
       <c r="I90" t="n">
-        <v>449.25</v>
+        <v>444.6</v>
       </c>
       <c r="J90" t="n">
-        <v>449.25</v>
+        <v>444.6</v>
       </c>
       <c r="K90" t="n">
         <v>0</v>
       </c>
       <c r="L90" t="n">
-        <v>455.7599999999998</v>
+        <v>451.11</v>
       </c>
       <c r="M90" t="n">
-        <v>458.28</v>
+        <v>453.6299999999998</v>
       </c>
       <c r="N90" t="n">
-        <v>504.7899999999997</v>
+        <v>500.1399999999997</v>
       </c>
     </row>
     <row r="91">
@@ -4802,22 +4802,22 @@
         <v>445</v>
       </c>
       <c r="I91" t="n">
-        <v>452.7</v>
+        <v>448.05</v>
       </c>
       <c r="J91" t="n">
-        <v>452.7</v>
+        <v>448.05</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>459.21</v>
+        <v>454.56</v>
       </c>
       <c r="M91" t="n">
-        <v>461.7299999999997</v>
+        <v>457.08</v>
       </c>
       <c r="N91" t="n">
-        <v>504.2099999999998</v>
+        <v>499.56</v>
       </c>
     </row>
     <row r="92">
@@ -4850,22 +4850,22 @@
         <v>450</v>
       </c>
       <c r="I92" t="n">
-        <v>456.15</v>
+        <v>451.5</v>
       </c>
       <c r="J92" t="n">
-        <v>456.15</v>
+        <v>451.5</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
       </c>
       <c r="L92" t="n">
-        <v>462.66</v>
+        <v>458.01</v>
       </c>
       <c r="M92" t="n">
-        <v>465.1799999999998</v>
+        <v>460.53</v>
       </c>
       <c r="N92" t="n">
-        <v>526.6899999999411</v>
+        <v>522.0399999999998</v>
       </c>
     </row>
     <row r="93">
@@ -4889,7 +4889,7 @@
         <v>91</v>
       </c>
       <c r="F93" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G93" t="n">
         <v>2</v>
@@ -4907,13 +4907,13 @@
         <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>466.1099999999998</v>
+        <v>466.11</v>
       </c>
       <c r="M93" t="n">
         <v>468.63</v>
       </c>
       <c r="N93" t="n">
-        <v>466.1099999999998</v>
+        <v>466.11</v>
       </c>
     </row>
     <row r="94">
@@ -4958,7 +4958,7 @@
         <v>469.56</v>
       </c>
       <c r="M94" t="n">
-        <v>472.0799999999998</v>
+        <v>472.08</v>
       </c>
       <c r="N94" t="n">
         <v>504.56</v>
@@ -4985,7 +4985,7 @@
         <v>93</v>
       </c>
       <c r="F95" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -5003,13 +5003,13 @@
         <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>473.0099999999998</v>
+        <v>473.01</v>
       </c>
       <c r="M95" t="n">
-        <v>475.5299999999998</v>
+        <v>475.5299999999997</v>
       </c>
       <c r="N95" t="n">
-        <v>508.0099999999998</v>
+        <v>508.0099999999999</v>
       </c>
     </row>
     <row r="96">
@@ -5033,7 +5033,7 @@
         <v>94</v>
       </c>
       <c r="F96" t="n">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G96" t="n">
         <v>5</v>
@@ -5042,22 +5042,22 @@
         <v>470</v>
       </c>
       <c r="I96" t="n">
-        <v>479.25</v>
+        <v>474.6</v>
       </c>
       <c r="J96" t="n">
-        <v>479.25</v>
+        <v>474.6</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>485.7599999999998</v>
+        <v>481.11</v>
       </c>
       <c r="M96" t="n">
-        <v>488.28</v>
+        <v>483.63</v>
       </c>
       <c r="N96" t="n">
-        <v>504.7899999999997</v>
+        <v>500.1399999999997</v>
       </c>
     </row>
     <row r="97">
@@ -5090,22 +5090,22 @@
         <v>475</v>
       </c>
       <c r="I97" t="n">
-        <v>482.7</v>
+        <v>478.05</v>
       </c>
       <c r="J97" t="n">
-        <v>482.7</v>
+        <v>478.05</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
       </c>
       <c r="L97" t="n">
-        <v>489.2099999999998</v>
+        <v>484.56</v>
       </c>
       <c r="M97" t="n">
-        <v>491.73</v>
+        <v>487.08</v>
       </c>
       <c r="N97" t="n">
-        <v>504.2099999999998</v>
+        <v>499.56</v>
       </c>
     </row>
     <row r="98">
@@ -5129,7 +5129,7 @@
         <v>96</v>
       </c>
       <c r="F98" t="n">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G98" t="n">
         <v>5</v>
@@ -5138,22 +5138,22 @@
         <v>480</v>
       </c>
       <c r="I98" t="n">
-        <v>489.25</v>
+        <v>484.6</v>
       </c>
       <c r="J98" t="n">
-        <v>489.25</v>
+        <v>484.6</v>
       </c>
       <c r="K98" t="n">
         <v>0</v>
       </c>
       <c r="L98" t="n">
-        <v>495.7599999999998</v>
+        <v>491.11</v>
       </c>
       <c r="M98" t="n">
-        <v>498.28</v>
+        <v>493.63</v>
       </c>
       <c r="N98" t="n">
-        <v>504.7899999999997</v>
+        <v>500.1399999999997</v>
       </c>
     </row>
     <row r="99">
@@ -5177,7 +5177,7 @@
         <v>97</v>
       </c>
       <c r="F99" t="n">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G99" t="n">
         <v>5</v>
@@ -5186,22 +5186,22 @@
         <v>485</v>
       </c>
       <c r="I99" t="n">
-        <v>494.25</v>
+        <v>489.6</v>
       </c>
       <c r="J99" t="n">
-        <v>498.2799999999998</v>
+        <v>493.6299999999998</v>
       </c>
       <c r="K99" t="n">
-        <v>4.029999999999802</v>
+        <v>4.029999999999745</v>
       </c>
       <c r="L99" t="n">
-        <v>504.7899999999998</v>
+        <v>500.1399999999998</v>
       </c>
       <c r="M99" t="n">
-        <v>507.31</v>
+        <v>502.6599999999997</v>
       </c>
       <c r="N99" t="n">
-        <v>504.7899999999997</v>
+        <v>500.1399999999997</v>
       </c>
     </row>
     <row r="100">
@@ -5234,22 +5234,22 @@
         <v>490</v>
       </c>
       <c r="I100" t="n">
-        <v>497.7</v>
+        <v>493.05</v>
       </c>
       <c r="J100" t="n">
-        <v>497.7</v>
+        <v>493.05</v>
       </c>
       <c r="K100" t="n">
         <v>0</v>
       </c>
       <c r="L100" t="n">
-        <v>504.2099999999998</v>
+        <v>499.56</v>
       </c>
       <c r="M100" t="n">
-        <v>506.7299999999998</v>
+        <v>502.08</v>
       </c>
       <c r="N100" t="n">
-        <v>504.2099999999998</v>
+        <v>499.56</v>
       </c>
     </row>
     <row r="101">
@@ -5294,7 +5294,7 @@
         <v>504.56</v>
       </c>
       <c r="M101" t="n">
-        <v>507.0799999999998</v>
+        <v>507.0799999999999</v>
       </c>
       <c r="N101" t="n">
         <v>504.56</v>
@@ -5321,7 +5321,7 @@
         <v>100</v>
       </c>
       <c r="F102" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -5339,13 +5339,13 @@
         <v>0</v>
       </c>
       <c r="L102" t="n">
-        <v>508.0099999999998</v>
+        <v>508.0099999999999</v>
       </c>
       <c r="M102" t="n">
-        <v>510.5299999999997</v>
+        <v>510.5299999999998</v>
       </c>
       <c r="N102" t="n">
-        <v>508.0099999999998</v>
+        <v>508.0099999999999</v>
       </c>
     </row>
     <row r="103">
@@ -5378,22 +5378,22 @@
         <v>505</v>
       </c>
       <c r="I103" t="n">
-        <v>511.15</v>
+        <v>506.5</v>
       </c>
       <c r="J103" t="n">
-        <v>511.15</v>
+        <v>506.5</v>
       </c>
       <c r="K103" t="n">
         <v>0</v>
       </c>
       <c r="L103" t="n">
-        <v>517.6599999999999</v>
+        <v>513.01</v>
       </c>
       <c r="M103" t="n">
-        <v>520.1799999999996</v>
+        <v>515.53</v>
       </c>
       <c r="N103" t="n">
-        <v>526.6899999999411</v>
+        <v>522.0399999999998</v>
       </c>
     </row>
     <row r="104">
@@ -5426,22 +5426,22 @@
         <v>510</v>
       </c>
       <c r="I104" t="n">
-        <v>516.15</v>
+        <v>511.5</v>
       </c>
       <c r="J104" t="n">
-        <v>520.1799999999411</v>
+        <v>515.5299999999999</v>
       </c>
       <c r="K104" t="n">
-        <v>4.029999999941083</v>
+        <v>4.029999999999859</v>
       </c>
       <c r="L104" t="n">
-        <v>526.6899999999411</v>
+        <v>522.0399999999998</v>
       </c>
       <c r="M104" t="n">
-        <v>529.209999999941</v>
+        <v>524.5599999999998</v>
       </c>
       <c r="N104" t="n">
-        <v>526.6899999999411</v>
+        <v>522.0399999999998</v>
       </c>
     </row>
   </sheetData>

--- a/MIP_RULE/results/model_B_piece_details.xlsx
+++ b/MIP_RULE/results/model_B_piece_details.xlsx
@@ -521,31 +521,31 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>3.05</v>
+        <v>4.6</v>
       </c>
       <c r="J2" t="n">
-        <v>3.05</v>
+        <v>4.6</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>8.390000000000001</v>
+        <v>9.94</v>
       </c>
       <c r="M2" t="n">
-        <v>9.720000000000001</v>
+        <v>11.27</v>
       </c>
       <c r="N2" t="n">
-        <v>8.390000000000001</v>
+        <v>9.94</v>
       </c>
     </row>
     <row r="3">
@@ -569,31 +569,31 @@
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>5</v>
       </c>
       <c r="I3" t="n">
-        <v>9.6</v>
+        <v>6.5</v>
       </c>
       <c r="J3" t="n">
-        <v>9.6</v>
+        <v>6.5</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>14.94</v>
+        <v>11.84</v>
       </c>
       <c r="M3" t="n">
-        <v>16.27</v>
+        <v>13.17</v>
       </c>
       <c r="N3" t="n">
-        <v>14.94</v>
+        <v>11.84</v>
       </c>
     </row>
     <row r="4">
@@ -617,31 +617,31 @@
         <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
         <v>10</v>
       </c>
       <c r="I4" t="n">
-        <v>14.6</v>
+        <v>13.05</v>
       </c>
       <c r="J4" t="n">
-        <v>14.6</v>
+        <v>13.05</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>19.94</v>
+        <v>18.3899999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>21.27</v>
+        <v>19.7199999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>19.94</v>
+        <v>18.3899999999999</v>
       </c>
     </row>
     <row r="5">
@@ -665,31 +665,31 @@
         <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
         <v>15</v>
       </c>
       <c r="I5" t="n">
-        <v>18.05</v>
+        <v>19.6</v>
       </c>
       <c r="J5" t="n">
-        <v>18.05</v>
+        <v>19.6</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>23.39</v>
+        <v>24.93999999999987</v>
       </c>
       <c r="M5" t="n">
-        <v>24.72</v>
+        <v>26.26999999999987</v>
       </c>
       <c r="N5" t="n">
-        <v>23.39</v>
+        <v>24.93999999999987</v>
       </c>
     </row>
     <row r="6">
@@ -713,10 +713,10 @@
         <v>4</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
         <v>20</v>
@@ -731,13 +731,13 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>26.84</v>
+        <v>26.83999999999987</v>
       </c>
       <c r="M6" t="n">
-        <v>28.17</v>
+        <v>28.16999999999987</v>
       </c>
       <c r="N6" t="n">
-        <v>26.84</v>
+        <v>26.83999999999987</v>
       </c>
     </row>
     <row r="7">
@@ -761,31 +761,31 @@
         <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
         <v>25</v>
       </c>
       <c r="I7" t="n">
-        <v>26.5</v>
+        <v>28.05</v>
       </c>
       <c r="J7" t="n">
-        <v>26.5</v>
+        <v>28.05</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>31.84</v>
+        <v>33.38999999999982</v>
       </c>
       <c r="M7" t="n">
-        <v>33.16999999999999</v>
+        <v>34.71999999999982</v>
       </c>
       <c r="N7" t="n">
-        <v>31.84</v>
+        <v>33.38999999999982</v>
       </c>
     </row>
     <row r="8">
@@ -827,13 +827,13 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>37.01</v>
+        <v>37.00999999999986</v>
       </c>
       <c r="M8" t="n">
-        <v>38.53</v>
+        <v>38.52999999999986</v>
       </c>
       <c r="N8" t="n">
-        <v>37.01</v>
+        <v>37.00999999999986</v>
       </c>
     </row>
     <row r="9">
@@ -875,13 +875,13 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>43.56</v>
+        <v>43.55999999999974</v>
       </c>
       <c r="M9" t="n">
-        <v>45.07999999999997</v>
+        <v>45.07999999999974</v>
       </c>
       <c r="N9" t="n">
-        <v>43.56</v>
+        <v>43.55999999999974</v>
       </c>
     </row>
     <row r="10">
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>50.11</v>
+        <v>50.1099999994812</v>
       </c>
       <c r="M10" t="n">
-        <v>51.62999999999999</v>
+        <v>51.6299999994812</v>
       </c>
       <c r="N10" t="n">
-        <v>50.11</v>
+        <v>50.1099999994812</v>
       </c>
     </row>
     <row r="11">
@@ -971,13 +971,13 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>52.00999999999996</v>
+        <v>52.00999999999891</v>
       </c>
       <c r="M11" t="n">
-        <v>53.52999999999997</v>
+        <v>53.52999999999891</v>
       </c>
       <c r="N11" t="n">
-        <v>52.00999999999996</v>
+        <v>52.00999999999891</v>
       </c>
     </row>
     <row r="12">
@@ -1019,13 +1019,13 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>58.56</v>
+        <v>58.55999999948842</v>
       </c>
       <c r="M12" t="n">
-        <v>60.07999999999998</v>
+        <v>60.07999999948842</v>
       </c>
       <c r="N12" t="n">
-        <v>58.56</v>
+        <v>58.55999999948842</v>
       </c>
     </row>
     <row r="13">
@@ -1067,13 +1067,13 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>65.11</v>
+        <v>65.10999999999812</v>
       </c>
       <c r="M13" t="n">
-        <v>66.63</v>
+        <v>66.62999999999812</v>
       </c>
       <c r="N13" t="n">
-        <v>65.11</v>
+        <v>65.10999999999812</v>
       </c>
     </row>
     <row r="14">
@@ -1115,13 +1115,13 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>67.31999999999999</v>
+        <v>67.31999999999972</v>
       </c>
       <c r="M14" t="n">
         <v>69.15000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>67.31999999999999</v>
+        <v>67.31999999999972</v>
       </c>
     </row>
     <row r="15">
@@ -1163,13 +1163,13 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>73.87</v>
+        <v>73.86999999999995</v>
       </c>
       <c r="M15" t="n">
         <v>75.7</v>
       </c>
       <c r="N15" t="n">
-        <v>73.87</v>
+        <v>73.86999999999995</v>
       </c>
     </row>
     <row r="16">
@@ -1211,13 +1211,13 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>80.41999999999999</v>
+        <v>80.41999999999996</v>
       </c>
       <c r="M16" t="n">
         <v>82.25</v>
       </c>
       <c r="N16" t="n">
-        <v>80.41999999999999</v>
+        <v>80.41999999999996</v>
       </c>
     </row>
     <row r="17">
@@ -1259,13 +1259,13 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>82.31999999999999</v>
+        <v>82.31999999999982</v>
       </c>
       <c r="M17" t="n">
         <v>84.15000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>82.31999999999999</v>
+        <v>82.31999999999982</v>
       </c>
     </row>
     <row r="18">
@@ -1307,13 +1307,13 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>88.87</v>
+        <v>88.86999999999995</v>
       </c>
       <c r="M18" t="n">
         <v>90.7</v>
       </c>
       <c r="N18" t="n">
-        <v>88.87</v>
+        <v>88.86999999999995</v>
       </c>
     </row>
     <row r="19">
@@ -1355,13 +1355,13 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>95.41999999999999</v>
+        <v>95.41999999999814</v>
       </c>
       <c r="M19" t="n">
         <v>97.25</v>
       </c>
       <c r="N19" t="n">
-        <v>95.41999999999999</v>
+        <v>95.41999999999814</v>
       </c>
     </row>
     <row r="20">
@@ -1403,13 +1403,13 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>97.31999999999999</v>
+        <v>97.31999999999994</v>
       </c>
       <c r="M20" t="n">
         <v>99.15000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>97.31999999999999</v>
+        <v>97.31999999999994</v>
       </c>
     </row>
     <row r="21">
@@ -1451,13 +1451,13 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>103.87</v>
+        <v>103.8699999999999</v>
       </c>
       <c r="M21" t="n">
         <v>105.7</v>
       </c>
       <c r="N21" t="n">
-        <v>103.87</v>
+        <v>103.8699999999999</v>
       </c>
     </row>
     <row r="22">
@@ -1547,13 +1547,13 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>112.32</v>
+        <v>112.3199999999998</v>
       </c>
       <c r="M23" t="n">
         <v>114.15</v>
       </c>
       <c r="N23" t="n">
-        <v>112.32</v>
+        <v>112.3199999999998</v>
       </c>
     </row>
     <row r="24">
@@ -1595,13 +1595,13 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>118.87</v>
+        <v>118.8699999999998</v>
       </c>
       <c r="M24" t="n">
         <v>120.7</v>
       </c>
       <c r="N24" t="n">
-        <v>118.87</v>
+        <v>118.8699999999998</v>
       </c>
     </row>
     <row r="25">
@@ -1643,13 +1643,13 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>125.42</v>
+        <v>125.4199999999975</v>
       </c>
       <c r="M25" t="n">
         <v>127.25</v>
       </c>
       <c r="N25" t="n">
-        <v>125.42</v>
+        <v>125.4199999999975</v>
       </c>
     </row>
     <row r="26">
@@ -1694,7 +1694,7 @@
         <v>127.35</v>
       </c>
       <c r="M26" t="n">
-        <v>129.19</v>
+        <v>129.1899999999999</v>
       </c>
       <c r="N26" t="n">
         <v>127.35</v>
@@ -1742,7 +1742,7 @@
         <v>133.9</v>
       </c>
       <c r="M27" t="n">
-        <v>135.74</v>
+        <v>135.7399999999972</v>
       </c>
       <c r="N27" t="n">
         <v>133.9</v>
@@ -1838,7 +1838,7 @@
         <v>142.35</v>
       </c>
       <c r="M29" t="n">
-        <v>144.19</v>
+        <v>144.1899999999998</v>
       </c>
       <c r="N29" t="n">
         <v>142.35</v>
@@ -1934,10 +1934,10 @@
         <v>155.45</v>
       </c>
       <c r="M31" t="n">
-        <v>157.29</v>
+        <v>157.2899999999998</v>
       </c>
       <c r="N31" t="n">
-        <v>163.14</v>
+        <v>163.1399999999998</v>
       </c>
     </row>
     <row r="32">
@@ -1973,19 +1973,19 @@
         <v>154.6</v>
       </c>
       <c r="J32" t="n">
-        <v>157.29</v>
+        <v>157.2899999999998</v>
       </c>
       <c r="K32" t="n">
-        <v>2.689999999999941</v>
+        <v>2.689999999999799</v>
       </c>
       <c r="L32" t="n">
-        <v>163.14</v>
+        <v>163.1399999999998</v>
       </c>
       <c r="M32" t="n">
-        <v>164.98</v>
+        <v>164.9799999999998</v>
       </c>
       <c r="N32" t="n">
-        <v>163.14</v>
+        <v>163.1399999999998</v>
       </c>
     </row>
     <row r="33">
@@ -2030,7 +2030,7 @@
         <v>162.35</v>
       </c>
       <c r="M33" t="n">
-        <v>164.19</v>
+        <v>164.1899999999999</v>
       </c>
       <c r="N33" t="n">
         <v>162.35</v>
@@ -2078,10 +2078,10 @@
         <v>168.9</v>
       </c>
       <c r="M34" t="n">
-        <v>170.74</v>
+        <v>170.7399999999997</v>
       </c>
       <c r="N34" t="n">
-        <v>176.59</v>
+        <v>176.5899999999997</v>
       </c>
     </row>
     <row r="35">
@@ -2117,19 +2117,19 @@
         <v>168.05</v>
       </c>
       <c r="J35" t="n">
-        <v>170.74</v>
+        <v>170.7399999999997</v>
       </c>
       <c r="K35" t="n">
-        <v>2.689999999999969</v>
+        <v>2.689999999999657</v>
       </c>
       <c r="L35" t="n">
-        <v>176.59</v>
+        <v>176.5899999999997</v>
       </c>
       <c r="M35" t="n">
-        <v>178.43</v>
+        <v>178.4299999999997</v>
       </c>
       <c r="N35" t="n">
-        <v>176.59</v>
+        <v>176.5899999999997</v>
       </c>
     </row>
     <row r="36">
@@ -2174,10 +2174,10 @@
         <v>180.45</v>
       </c>
       <c r="M36" t="n">
-        <v>182.29</v>
+        <v>182.2899999999998</v>
       </c>
       <c r="N36" t="n">
-        <v>188.14</v>
+        <v>188.1399999999998</v>
       </c>
     </row>
     <row r="37">
@@ -2213,19 +2213,19 @@
         <v>179.6</v>
       </c>
       <c r="J37" t="n">
-        <v>182.29</v>
+        <v>182.2899999999998</v>
       </c>
       <c r="K37" t="n">
-        <v>2.689999999999969</v>
+        <v>2.689999999999742</v>
       </c>
       <c r="L37" t="n">
-        <v>188.14</v>
+        <v>188.1399999999998</v>
       </c>
       <c r="M37" t="n">
-        <v>189.98</v>
+        <v>189.9799999999998</v>
       </c>
       <c r="N37" t="n">
-        <v>188.14</v>
+        <v>188.1399999999998</v>
       </c>
     </row>
     <row r="38">
@@ -2270,7 +2270,7 @@
         <v>187.35</v>
       </c>
       <c r="M38" t="n">
-        <v>189.1899999999997</v>
+        <v>189.1899999999998</v>
       </c>
       <c r="N38" t="n">
         <v>187.35</v>
@@ -2318,7 +2318,7 @@
         <v>193.9</v>
       </c>
       <c r="M39" t="n">
-        <v>195.74</v>
+        <v>195.7399999999999</v>
       </c>
       <c r="N39" t="n">
         <v>193.9</v>
@@ -2366,7 +2366,7 @@
         <v>200.45</v>
       </c>
       <c r="M40" t="n">
-        <v>202.2899999999999</v>
+        <v>202.2899999999998</v>
       </c>
       <c r="N40" t="n">
         <v>200.45</v>
@@ -2411,13 +2411,13 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>202.68</v>
+        <v>202.6799999999998</v>
       </c>
       <c r="M41" t="n">
-        <v>204.86</v>
+        <v>204.8599999999998</v>
       </c>
       <c r="N41" t="n">
-        <v>202.68</v>
+        <v>202.6799999999998</v>
       </c>
     </row>
     <row r="42">
@@ -2459,13 +2459,13 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>209.23</v>
+        <v>209.2299999999999</v>
       </c>
       <c r="M42" t="n">
-        <v>211.41</v>
+        <v>211.4099999999999</v>
       </c>
       <c r="N42" t="n">
-        <v>209.23</v>
+        <v>209.2299999999999</v>
       </c>
     </row>
     <row r="43">
@@ -2507,13 +2507,13 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>215.78</v>
+        <v>215.7799999999998</v>
       </c>
       <c r="M43" t="n">
-        <v>217.96</v>
+        <v>217.9599999999998</v>
       </c>
       <c r="N43" t="n">
-        <v>215.78</v>
+        <v>215.7799999999998</v>
       </c>
     </row>
     <row r="44">
@@ -2555,13 +2555,13 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>217.68</v>
+        <v>217.6799999999998</v>
       </c>
       <c r="M44" t="n">
-        <v>219.86</v>
+        <v>219.8599999999998</v>
       </c>
       <c r="N44" t="n">
-        <v>217.68</v>
+        <v>217.6799999999998</v>
       </c>
     </row>
     <row r="45">
@@ -2603,13 +2603,13 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>224.23</v>
+        <v>224.2299999999999</v>
       </c>
       <c r="M45" t="n">
-        <v>226.41</v>
+        <v>226.4099999999999</v>
       </c>
       <c r="N45" t="n">
-        <v>224.23</v>
+        <v>224.2299999999999</v>
       </c>
     </row>
     <row r="46">
@@ -2651,13 +2651,13 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>230.78</v>
+        <v>230.7799999999984</v>
       </c>
       <c r="M46" t="n">
-        <v>232.9599999999999</v>
+        <v>232.9599999999984</v>
       </c>
       <c r="N46" t="n">
-        <v>230.78</v>
+        <v>230.7799999999984</v>
       </c>
     </row>
     <row r="47">
@@ -2699,13 +2699,13 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>232.68</v>
+        <v>232.6799999999999</v>
       </c>
       <c r="M47" t="n">
-        <v>234.86</v>
+        <v>234.8599999999999</v>
       </c>
       <c r="N47" t="n">
-        <v>232.68</v>
+        <v>232.6799999999999</v>
       </c>
     </row>
     <row r="48">
@@ -2747,13 +2747,13 @@
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>239.23</v>
+        <v>239.2299999999999</v>
       </c>
       <c r="M48" t="n">
-        <v>241.41</v>
+        <v>241.4099999999999</v>
       </c>
       <c r="N48" t="n">
-        <v>239.23</v>
+        <v>239.2299999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2795,13 +2795,13 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>245.78</v>
+        <v>245.7799999999998</v>
       </c>
       <c r="M49" t="n">
-        <v>247.96</v>
+        <v>247.9599999999998</v>
       </c>
       <c r="N49" t="n">
-        <v>245.78</v>
+        <v>245.7799999999998</v>
       </c>
     </row>
     <row r="50">
@@ -2843,13 +2843,13 @@
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>247.68</v>
+        <v>247.6799999999996</v>
       </c>
       <c r="M50" t="n">
-        <v>249.86</v>
+        <v>249.8599999999996</v>
       </c>
       <c r="N50" t="n">
-        <v>247.68</v>
+        <v>247.6799999999996</v>
       </c>
     </row>
     <row r="51">
@@ -2891,13 +2891,13 @@
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>254.23</v>
+        <v>254.2299999999996</v>
       </c>
       <c r="M51" t="n">
-        <v>256.41</v>
+        <v>256.4099999999996</v>
       </c>
       <c r="N51" t="n">
-        <v>254.23</v>
+        <v>254.2299999999996</v>
       </c>
     </row>
     <row r="52">
@@ -2939,13 +2939,13 @@
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>260.78</v>
+        <v>260.7799999999996</v>
       </c>
       <c r="M52" t="n">
-        <v>262.96</v>
+        <v>262.9599999999996</v>
       </c>
       <c r="N52" t="n">
-        <v>269.14</v>
+        <v>269.1399999999995</v>
       </c>
     </row>
     <row r="53">
@@ -2981,19 +2981,19 @@
         <v>259.6</v>
       </c>
       <c r="J53" t="n">
-        <v>262.96</v>
+        <v>262.9599999999996</v>
       </c>
       <c r="K53" t="n">
-        <v>3.359999999999957</v>
+        <v>3.359999999999559</v>
       </c>
       <c r="L53" t="n">
-        <v>269.14</v>
+        <v>269.1399999999996</v>
       </c>
       <c r="M53" t="n">
-        <v>271.32</v>
+        <v>271.3199999999996</v>
       </c>
       <c r="N53" t="n">
-        <v>269.14</v>
+        <v>269.1399999999995</v>
       </c>
     </row>
     <row r="54">
@@ -3035,13 +3035,13 @@
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>267.81</v>
+        <v>267.8099999999999</v>
       </c>
       <c r="M54" t="n">
-        <v>270.13</v>
+        <v>270.1299999999999</v>
       </c>
       <c r="N54" t="n">
-        <v>267.81</v>
+        <v>267.8099999999999</v>
       </c>
     </row>
     <row r="55">
@@ -3083,13 +3083,13 @@
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>274.36</v>
+        <v>274.3599999999998</v>
       </c>
       <c r="M55" t="n">
-        <v>276.68</v>
+        <v>276.6799999999998</v>
       </c>
       <c r="N55" t="n">
-        <v>274.36</v>
+        <v>274.3599999999998</v>
       </c>
     </row>
     <row r="56">
@@ -3113,7 +3113,7 @@
         <v>54</v>
       </c>
       <c r="F56" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G56" t="n">
         <v>2</v>
@@ -3131,13 +3131,13 @@
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>280.91</v>
+        <v>280.9099999999999</v>
       </c>
       <c r="M56" t="n">
-        <v>283.23</v>
+        <v>283.2299999999999</v>
       </c>
       <c r="N56" t="n">
-        <v>280.91</v>
+        <v>280.9099999999999</v>
       </c>
     </row>
     <row r="57">
@@ -3161,7 +3161,7 @@
         <v>55</v>
       </c>
       <c r="F57" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G57" t="n">
         <v>3</v>
@@ -3179,13 +3179,13 @@
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>282.81</v>
+        <v>282.8099999999998</v>
       </c>
       <c r="M57" t="n">
-        <v>285.13</v>
+        <v>285.1299999999998</v>
       </c>
       <c r="N57" t="n">
-        <v>282.81</v>
+        <v>282.8099999999998</v>
       </c>
     </row>
     <row r="58">
@@ -3227,13 +3227,13 @@
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>289.36</v>
+        <v>289.3599999999997</v>
       </c>
       <c r="M58" t="n">
-        <v>291.68</v>
+        <v>291.6799999999997</v>
       </c>
       <c r="N58" t="n">
-        <v>289.36</v>
+        <v>289.3599999999997</v>
       </c>
     </row>
     <row r="59">
@@ -3275,13 +3275,13 @@
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>295.91</v>
+        <v>295.9099999999996</v>
       </c>
       <c r="M59" t="n">
-        <v>298.23</v>
+        <v>298.2299999999996</v>
       </c>
       <c r="N59" t="n">
-        <v>295.91</v>
+        <v>295.9099999999996</v>
       </c>
     </row>
     <row r="60">
@@ -3323,13 +3323,13 @@
         <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>297.81</v>
+        <v>297.8099999999998</v>
       </c>
       <c r="M60" t="n">
-        <v>300.13</v>
+        <v>300.1299999999998</v>
       </c>
       <c r="N60" t="n">
-        <v>297.81</v>
+        <v>297.8099999999998</v>
       </c>
     </row>
     <row r="61">
@@ -3371,13 +3371,13 @@
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>304.36</v>
+        <v>304.3599999999999</v>
       </c>
       <c r="M61" t="n">
-        <v>306.68</v>
+        <v>306.6799999999999</v>
       </c>
       <c r="N61" t="n">
-        <v>304.36</v>
+        <v>304.3599999999999</v>
       </c>
     </row>
     <row r="62">
@@ -3401,10 +3401,10 @@
         <v>60</v>
       </c>
       <c r="F62" t="n">
-        <v>41</v>
+        <v>87</v>
       </c>
       <c r="G62" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H62" t="n">
         <v>300</v>
@@ -3449,31 +3449,31 @@
         <v>61</v>
       </c>
       <c r="F63" t="n">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="G63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H63" t="n">
         <v>305</v>
       </c>
       <c r="I63" t="n">
-        <v>306.5</v>
+        <v>309.6</v>
       </c>
       <c r="J63" t="n">
-        <v>306.5</v>
+        <v>309.6</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>312.81</v>
+        <v>315.91</v>
       </c>
       <c r="M63" t="n">
-        <v>315.13</v>
+        <v>318.23</v>
       </c>
       <c r="N63" t="n">
-        <v>312.81</v>
+        <v>315.91</v>
       </c>
     </row>
     <row r="64">
@@ -3518,7 +3518,7 @@
         <v>319.36</v>
       </c>
       <c r="M64" t="n">
-        <v>321.68</v>
+        <v>321.6799999999998</v>
       </c>
       <c r="N64" t="n">
         <v>319.36</v>
@@ -3545,31 +3545,31 @@
         <v>63</v>
       </c>
       <c r="F65" t="n">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="G65" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H65" t="n">
         <v>315</v>
       </c>
       <c r="I65" t="n">
-        <v>319.6</v>
+        <v>316.5</v>
       </c>
       <c r="J65" t="n">
-        <v>319.6</v>
+        <v>316.5</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>325.9099999999997</v>
+        <v>322.8099999999999</v>
       </c>
       <c r="M65" t="n">
-        <v>328.2299999999997</v>
+        <v>325.1299999999995</v>
       </c>
       <c r="N65" t="n">
-        <v>325.9099999999997</v>
+        <v>322.8099999999999</v>
       </c>
     </row>
     <row r="66">
@@ -3611,13 +3611,13 @@
         <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>327.81</v>
+        <v>327.8099999999999</v>
       </c>
       <c r="M66" t="n">
-        <v>330.13</v>
+        <v>330.1299999999999</v>
       </c>
       <c r="N66" t="n">
-        <v>327.81</v>
+        <v>327.8099999999999</v>
       </c>
     </row>
     <row r="67">
@@ -3659,13 +3659,13 @@
         <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>334.36</v>
+        <v>334.3599999999999</v>
       </c>
       <c r="M67" t="n">
-        <v>336.68</v>
+        <v>336.6799999999999</v>
       </c>
       <c r="N67" t="n">
-        <v>334.36</v>
+        <v>334.3599999999999</v>
       </c>
     </row>
     <row r="68">
@@ -3689,10 +3689,10 @@
         <v>66</v>
       </c>
       <c r="F68" t="n">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="G68" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H68" t="n">
         <v>330</v>
@@ -3710,7 +3710,7 @@
         <v>340.91</v>
       </c>
       <c r="M68" t="n">
-        <v>343.23</v>
+        <v>343.2299999999997</v>
       </c>
       <c r="N68" t="n">
         <v>340.91</v>
@@ -3737,7 +3737,7 @@
         <v>67</v>
       </c>
       <c r="F69" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G69" t="n">
         <v>3</v>
@@ -3755,13 +3755,13 @@
         <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>342.81</v>
+        <v>342.8099999999999</v>
       </c>
       <c r="M69" t="n">
-        <v>345.13</v>
+        <v>345.1299999999999</v>
       </c>
       <c r="N69" t="n">
-        <v>342.81</v>
+        <v>342.8099999999999</v>
       </c>
     </row>
     <row r="70">
@@ -3803,13 +3803,13 @@
         <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>349.36</v>
+        <v>349.3599999999997</v>
       </c>
       <c r="M70" t="n">
-        <v>351.6799999999999</v>
+        <v>351.6799999999997</v>
       </c>
       <c r="N70" t="n">
-        <v>349.36</v>
+        <v>349.3599999999997</v>
       </c>
     </row>
     <row r="71">
@@ -3833,10 +3833,10 @@
         <v>69</v>
       </c>
       <c r="F71" t="n">
-        <v>87</v>
+        <v>42</v>
       </c>
       <c r="G71" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H71" t="n">
         <v>345</v>
@@ -3854,7 +3854,7 @@
         <v>355.91</v>
       </c>
       <c r="M71" t="n">
-        <v>358.2299999999999</v>
+        <v>358.2299999999998</v>
       </c>
       <c r="N71" t="n">
         <v>355.91</v>
@@ -3899,13 +3899,13 @@
         <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>357.81</v>
+        <v>357.8099999999998</v>
       </c>
       <c r="M72" t="n">
-        <v>360.13</v>
+        <v>360.1299999999998</v>
       </c>
       <c r="N72" t="n">
-        <v>357.81</v>
+        <v>357.8099999999998</v>
       </c>
     </row>
     <row r="73">
@@ -3947,13 +3947,13 @@
         <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>364.36</v>
+        <v>364.3599999999998</v>
       </c>
       <c r="M73" t="n">
-        <v>366.6799999999999</v>
+        <v>366.6799999999998</v>
       </c>
       <c r="N73" t="n">
-        <v>364.36</v>
+        <v>364.3599999999998</v>
       </c>
     </row>
     <row r="74">
@@ -3977,7 +3977,7 @@
         <v>72</v>
       </c>
       <c r="F74" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G74" t="n">
         <v>2</v>
@@ -3998,7 +3998,7 @@
         <v>370.91</v>
       </c>
       <c r="M74" t="n">
-        <v>373.2299999999999</v>
+        <v>373.23</v>
       </c>
       <c r="N74" t="n">
         <v>370.91</v>
@@ -4043,13 +4043,13 @@
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>372.81</v>
+        <v>372.8099999999996</v>
       </c>
       <c r="M75" t="n">
-        <v>375.13</v>
+        <v>375.1299999999996</v>
       </c>
       <c r="N75" t="n">
-        <v>372.81</v>
+        <v>372.8099999999996</v>
       </c>
     </row>
     <row r="76">
@@ -4091,13 +4091,13 @@
         <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>379.36</v>
+        <v>379.3599999999998</v>
       </c>
       <c r="M76" t="n">
-        <v>381.6799999999999</v>
+        <v>381.6799999999998</v>
       </c>
       <c r="N76" t="n">
-        <v>379.36</v>
+        <v>379.3599999999998</v>
       </c>
     </row>
     <row r="77">
@@ -4139,13 +4139,13 @@
         <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>385.91</v>
+        <v>385.9099999999999</v>
       </c>
       <c r="M77" t="n">
-        <v>388.2299999999999</v>
+        <v>388.2299999999998</v>
       </c>
       <c r="N77" t="n">
-        <v>385.91</v>
+        <v>385.9099999999999</v>
       </c>
     </row>
     <row r="78">
@@ -4169,31 +4169,31 @@
         <v>76</v>
       </c>
       <c r="F78" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="G78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H78" t="n">
         <v>380</v>
       </c>
       <c r="I78" t="n">
-        <v>383.05</v>
+        <v>384.6</v>
       </c>
       <c r="J78" t="n">
-        <v>383.05</v>
+        <v>384.6</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>389.56</v>
+        <v>391.11</v>
       </c>
       <c r="M78" t="n">
-        <v>392.08</v>
+        <v>393.6299999999989</v>
       </c>
       <c r="N78" t="n">
-        <v>389.56</v>
+        <v>391.11</v>
       </c>
     </row>
     <row r="79">
@@ -4217,31 +4217,31 @@
         <v>77</v>
       </c>
       <c r="F79" t="n">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="G79" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H79" t="n">
         <v>385</v>
       </c>
       <c r="I79" t="n">
-        <v>389.6</v>
+        <v>388.05</v>
       </c>
       <c r="J79" t="n">
-        <v>389.6</v>
+        <v>388.05</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>396.11</v>
+        <v>394.56</v>
       </c>
       <c r="M79" t="n">
-        <v>398.63</v>
+        <v>397.08</v>
       </c>
       <c r="N79" t="n">
-        <v>396.11</v>
+        <v>394.56</v>
       </c>
     </row>
     <row r="80">
@@ -4283,13 +4283,13 @@
         <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>398.01</v>
+        <v>398.0099999999998</v>
       </c>
       <c r="M80" t="n">
-        <v>400.53</v>
+        <v>400.5299999999997</v>
       </c>
       <c r="N80" t="n">
-        <v>398.01</v>
+        <v>398.0099999999998</v>
       </c>
     </row>
     <row r="81">
@@ -4313,10 +4313,10 @@
         <v>79</v>
       </c>
       <c r="F81" t="n">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="G81" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H81" t="n">
         <v>395</v>
@@ -4334,7 +4334,7 @@
         <v>406.11</v>
       </c>
       <c r="M81" t="n">
-        <v>408.63</v>
+        <v>408.6299999999995</v>
       </c>
       <c r="N81" t="n">
         <v>406.11</v>
@@ -4361,10 +4361,10 @@
         <v>80</v>
       </c>
       <c r="F82" t="n">
-        <v>74</v>
+        <v>19</v>
       </c>
       <c r="G82" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H82" t="n">
         <v>400</v>
@@ -4379,13 +4379,13 @@
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>409.56</v>
+        <v>409.5599999999998</v>
       </c>
       <c r="M82" t="n">
-        <v>412.0799999999999</v>
+        <v>412.0799999999998</v>
       </c>
       <c r="N82" t="n">
-        <v>409.56</v>
+        <v>409.5599999999998</v>
       </c>
     </row>
     <row r="83">
@@ -4427,13 +4427,13 @@
         <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>413.01</v>
+        <v>413.0099999999998</v>
       </c>
       <c r="M83" t="n">
-        <v>415.5299999999999</v>
+        <v>415.5299999999997</v>
       </c>
       <c r="N83" t="n">
-        <v>413.01</v>
+        <v>413.0099999999998</v>
       </c>
     </row>
     <row r="84">
@@ -4457,7 +4457,7 @@
         <v>82</v>
       </c>
       <c r="F84" t="n">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="G84" t="n">
         <v>5</v>
@@ -4478,7 +4478,7 @@
         <v>421.11</v>
       </c>
       <c r="M84" t="n">
-        <v>423.63</v>
+        <v>423.6299999999997</v>
       </c>
       <c r="N84" t="n">
         <v>421.11</v>
@@ -4505,31 +4505,31 @@
         <v>83</v>
       </c>
       <c r="F85" t="n">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="G85" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H85" t="n">
         <v>415</v>
       </c>
       <c r="I85" t="n">
-        <v>418.05</v>
+        <v>416.5</v>
       </c>
       <c r="J85" t="n">
-        <v>418.05</v>
+        <v>416.5</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>424.56</v>
+        <v>423.0099999999999</v>
       </c>
       <c r="M85" t="n">
-        <v>427.08</v>
+        <v>425.5299999999995</v>
       </c>
       <c r="N85" t="n">
-        <v>424.56</v>
+        <v>423.0099999999999</v>
       </c>
     </row>
     <row r="86">
@@ -4553,31 +4553,31 @@
         <v>84</v>
       </c>
       <c r="F86" t="n">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="G86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H86" t="n">
         <v>420</v>
       </c>
       <c r="I86" t="n">
-        <v>421.5</v>
+        <v>424.6</v>
       </c>
       <c r="J86" t="n">
-        <v>421.5</v>
+        <v>424.6</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>428.01</v>
+        <v>431.11</v>
       </c>
       <c r="M86" t="n">
-        <v>430.53</v>
+        <v>433.6299999999994</v>
       </c>
       <c r="N86" t="n">
-        <v>428.01</v>
+        <v>431.11</v>
       </c>
     </row>
     <row r="87">
@@ -4601,31 +4601,31 @@
         <v>85</v>
       </c>
       <c r="F87" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="G87" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H87" t="n">
         <v>425</v>
       </c>
       <c r="I87" t="n">
-        <v>429.6</v>
+        <v>428.05</v>
       </c>
       <c r="J87" t="n">
-        <v>429.6</v>
+        <v>428.05</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
       </c>
       <c r="L87" t="n">
-        <v>436.11</v>
+        <v>434.56</v>
       </c>
       <c r="M87" t="n">
-        <v>438.63</v>
+        <v>437.0799999999998</v>
       </c>
       <c r="N87" t="n">
-        <v>436.11</v>
+        <v>434.56</v>
       </c>
     </row>
     <row r="88">
@@ -4649,7 +4649,7 @@
         <v>86</v>
       </c>
       <c r="F88" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G88" t="n">
         <v>1</v>
@@ -4667,13 +4667,13 @@
         <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>439.56</v>
+        <v>439.5599999999998</v>
       </c>
       <c r="M88" t="n">
-        <v>442.08</v>
+        <v>442.0799999999998</v>
       </c>
       <c r="N88" t="n">
-        <v>439.56</v>
+        <v>439.5599999999998</v>
       </c>
     </row>
     <row r="89">
@@ -4715,13 +4715,13 @@
         <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>443.0099999999994</v>
+        <v>443.0099999999998</v>
       </c>
       <c r="M89" t="n">
-        <v>445.5299999999994</v>
+        <v>445.5299999999997</v>
       </c>
       <c r="N89" t="n">
-        <v>443.0099999999994</v>
+        <v>443.0099999999998</v>
       </c>
     </row>
     <row r="90">
@@ -4745,7 +4745,7 @@
         <v>88</v>
       </c>
       <c r="F90" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G90" t="n">
         <v>5</v>
@@ -4763,13 +4763,13 @@
         <v>0</v>
       </c>
       <c r="L90" t="n">
-        <v>451.11</v>
+        <v>451.1099999999994</v>
       </c>
       <c r="M90" t="n">
-        <v>453.6299999999998</v>
+        <v>453.6299999999994</v>
       </c>
       <c r="N90" t="n">
-        <v>500.1399999999997</v>
+        <v>500.1399999999996</v>
       </c>
     </row>
     <row r="91">
@@ -4793,7 +4793,7 @@
         <v>89</v>
       </c>
       <c r="F91" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G91" t="n">
         <v>4</v>
@@ -4805,19 +4805,19 @@
         <v>448.05</v>
       </c>
       <c r="J91" t="n">
-        <v>448.05</v>
+        <v>474.9899999999998</v>
       </c>
       <c r="K91" t="n">
-        <v>0</v>
+        <v>26.93999999999977</v>
       </c>
       <c r="L91" t="n">
-        <v>454.56</v>
+        <v>481.5</v>
       </c>
       <c r="M91" t="n">
-        <v>457.08</v>
+        <v>484.0199999999998</v>
       </c>
       <c r="N91" t="n">
-        <v>499.56</v>
+        <v>499.5599999999997</v>
       </c>
     </row>
     <row r="92">
@@ -4841,7 +4841,7 @@
         <v>90</v>
       </c>
       <c r="F92" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G92" t="n">
         <v>3</v>
@@ -4862,10 +4862,10 @@
         <v>458.01</v>
       </c>
       <c r="M92" t="n">
-        <v>460.53</v>
+        <v>460.5299999999998</v>
       </c>
       <c r="N92" t="n">
-        <v>522.0399999999998</v>
+        <v>522.0399999999995</v>
       </c>
     </row>
     <row r="93">
@@ -4889,7 +4889,7 @@
         <v>91</v>
       </c>
       <c r="F93" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G93" t="n">
         <v>2</v>
@@ -4910,7 +4910,7 @@
         <v>466.11</v>
       </c>
       <c r="M93" t="n">
-        <v>468.63</v>
+        <v>468.6299999999994</v>
       </c>
       <c r="N93" t="n">
         <v>466.11</v>
@@ -4937,7 +4937,7 @@
         <v>92</v>
       </c>
       <c r="F94" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G94" t="n">
         <v>1</v>
@@ -4955,10 +4955,10 @@
         <v>0</v>
       </c>
       <c r="L94" t="n">
-        <v>469.56</v>
+        <v>469.5599999999998</v>
       </c>
       <c r="M94" t="n">
-        <v>472.08</v>
+        <v>472.0799999999992</v>
       </c>
       <c r="N94" t="n">
         <v>504.56</v>
@@ -5003,13 +5003,13 @@
         <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>473.01</v>
+        <v>473.0099999999996</v>
       </c>
       <c r="M95" t="n">
-        <v>475.5299999999997</v>
+        <v>475.5299999999996</v>
       </c>
       <c r="N95" t="n">
-        <v>508.0099999999999</v>
+        <v>508.0099999999996</v>
       </c>
     </row>
     <row r="96">
@@ -5033,7 +5033,7 @@
         <v>94</v>
       </c>
       <c r="F96" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G96" t="n">
         <v>5</v>
@@ -5045,19 +5045,19 @@
         <v>474.6</v>
       </c>
       <c r="J96" t="n">
-        <v>474.6</v>
+        <v>475.5699999999997</v>
       </c>
       <c r="K96" t="n">
-        <v>0</v>
+        <v>0.9699999999996862</v>
       </c>
       <c r="L96" t="n">
-        <v>481.11</v>
+        <v>482.0799999999997</v>
       </c>
       <c r="M96" t="n">
-        <v>483.63</v>
+        <v>484.6</v>
       </c>
       <c r="N96" t="n">
-        <v>500.1399999999997</v>
+        <v>500.1399999999996</v>
       </c>
     </row>
     <row r="97">
@@ -5081,7 +5081,7 @@
         <v>95</v>
       </c>
       <c r="F97" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G97" t="n">
         <v>4</v>
@@ -5093,19 +5093,19 @@
         <v>478.05</v>
       </c>
       <c r="J97" t="n">
-        <v>478.05</v>
+        <v>484.0199999999998</v>
       </c>
       <c r="K97" t="n">
-        <v>0</v>
+        <v>5.969999999999743</v>
       </c>
       <c r="L97" t="n">
-        <v>484.56</v>
+        <v>490.5299999999997</v>
       </c>
       <c r="M97" t="n">
-        <v>487.08</v>
+        <v>493.05</v>
       </c>
       <c r="N97" t="n">
-        <v>499.56</v>
+        <v>499.5599999999997</v>
       </c>
     </row>
     <row r="98">
@@ -5129,7 +5129,7 @@
         <v>96</v>
       </c>
       <c r="F98" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G98" t="n">
         <v>5</v>
@@ -5147,13 +5147,13 @@
         <v>0</v>
       </c>
       <c r="L98" t="n">
-        <v>491.11</v>
+        <v>491.1099999999997</v>
       </c>
       <c r="M98" t="n">
-        <v>493.63</v>
+        <v>493.6299999999997</v>
       </c>
       <c r="N98" t="n">
-        <v>500.1399999999997</v>
+        <v>500.1399999999996</v>
       </c>
     </row>
     <row r="99">
@@ -5177,7 +5177,7 @@
         <v>97</v>
       </c>
       <c r="F99" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G99" t="n">
         <v>5</v>
@@ -5189,19 +5189,19 @@
         <v>489.6</v>
       </c>
       <c r="J99" t="n">
-        <v>493.6299999999998</v>
+        <v>493.6299999999996</v>
       </c>
       <c r="K99" t="n">
-        <v>4.029999999999745</v>
+        <v>4.029999999999575</v>
       </c>
       <c r="L99" t="n">
-        <v>500.1399999999998</v>
+        <v>500.1399999999996</v>
       </c>
       <c r="M99" t="n">
-        <v>502.6599999999997</v>
+        <v>502.6599999999996</v>
       </c>
       <c r="N99" t="n">
-        <v>500.1399999999997</v>
+        <v>500.1399999999996</v>
       </c>
     </row>
     <row r="100">
@@ -5225,7 +5225,7 @@
         <v>98</v>
       </c>
       <c r="F100" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G100" t="n">
         <v>4</v>
@@ -5243,13 +5243,13 @@
         <v>0</v>
       </c>
       <c r="L100" t="n">
-        <v>499.56</v>
+        <v>499.5599999999997</v>
       </c>
       <c r="M100" t="n">
-        <v>502.08</v>
+        <v>502.0799999999997</v>
       </c>
       <c r="N100" t="n">
-        <v>499.56</v>
+        <v>499.5599999999997</v>
       </c>
     </row>
     <row r="101">
@@ -5273,7 +5273,7 @@
         <v>99</v>
       </c>
       <c r="F101" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G101" t="n">
         <v>1</v>
@@ -5294,7 +5294,7 @@
         <v>504.56</v>
       </c>
       <c r="M101" t="n">
-        <v>507.0799999999999</v>
+        <v>507.08</v>
       </c>
       <c r="N101" t="n">
         <v>504.56</v>
@@ -5339,13 +5339,13 @@
         <v>0</v>
       </c>
       <c r="L102" t="n">
-        <v>508.0099999999999</v>
+        <v>508.0099999999996</v>
       </c>
       <c r="M102" t="n">
-        <v>510.5299999999998</v>
+        <v>510.5299999999996</v>
       </c>
       <c r="N102" t="n">
-        <v>508.0099999999999</v>
+        <v>508.0099999999996</v>
       </c>
     </row>
     <row r="103">
@@ -5369,7 +5369,7 @@
         <v>101</v>
       </c>
       <c r="F103" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G103" t="n">
         <v>3</v>
@@ -5393,7 +5393,7 @@
         <v>515.53</v>
       </c>
       <c r="N103" t="n">
-        <v>522.0399999999998</v>
+        <v>522.0399999999995</v>
       </c>
     </row>
     <row r="104">
@@ -5417,7 +5417,7 @@
         <v>101</v>
       </c>
       <c r="F104" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G104" t="n">
         <v>3</v>
@@ -5429,19 +5429,19 @@
         <v>511.5</v>
       </c>
       <c r="J104" t="n">
-        <v>515.5299999999999</v>
+        <v>515.5299999999995</v>
       </c>
       <c r="K104" t="n">
-        <v>4.029999999999859</v>
+        <v>4.029999999999518</v>
       </c>
       <c r="L104" t="n">
-        <v>522.0399999999998</v>
+        <v>522.0399999999995</v>
       </c>
       <c r="M104" t="n">
-        <v>524.5599999999998</v>
+        <v>524.5599999999995</v>
       </c>
       <c r="N104" t="n">
-        <v>522.0399999999998</v>
+        <v>522.0399999999995</v>
       </c>
     </row>
   </sheetData>
